--- a/dataset/results/loo_12_models.xlsx
+++ b/dataset/results/loo_12_models.xlsx
@@ -492,10 +492,10 @@
         <v>0.9969674094127446</v>
       </c>
       <c r="I2">
-        <v>0.00600819200190017</v>
+        <v>0.006491509000625229</v>
       </c>
       <c r="J2">
-        <v>0.6650210456873352</v>
+        <v>0.7906894134808978</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -524,10 +524,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>0.09338010999999824</v>
+        <v>0.0978955800019321</v>
       </c>
       <c r="J3">
-        <v>16.04351530668468</v>
+        <v>15.86525382774606</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -556,10 +556,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I4">
-        <v>0.09677231299792766</v>
+        <v>0.1132245099979627</v>
       </c>
       <c r="J4">
-        <v>2.78566326461278</v>
+        <v>2.402903062050298</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -588,10 +588,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I5">
-        <v>0.1902741199992306</v>
+        <v>0.1855527580009948</v>
       </c>
       <c r="J5">
-        <v>1.48218877563281</v>
+        <v>1.193208546208887</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -620,10 +620,10 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0.009209677999024279</v>
+        <v>0.0104402190008841</v>
       </c>
       <c r="J6">
-        <v>0.7472608419392396</v>
+        <v>0.8198443867736295</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>0.1146792990002723</v>
+        <v>0.1336346290008805</v>
       </c>
       <c r="J7">
-        <v>16.92254017960257</v>
+        <v>16.93507525552767</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -684,10 +684,10 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.1025782559991057</v>
+        <v>0.09943619399928139</v>
       </c>
       <c r="J8">
-        <v>2.514958544693678</v>
+        <v>2.491589287144182</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -716,10 +716,10 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0.1168408960002125</v>
+        <v>0.1137324099981925</v>
       </c>
       <c r="J9">
-        <v>1.061401147181845</v>
+        <v>1.124483418959931</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -748,10 +748,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I10">
-        <v>0.004317555998568423</v>
+        <v>0.004326718000811525</v>
       </c>
       <c r="J10">
-        <v>0.7948112225880768</v>
+        <v>0.771987244234526</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -780,10 +780,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I11">
-        <v>0.04499398400002974</v>
+        <v>0.0500231129990425</v>
       </c>
       <c r="J11">
-        <v>4.760867983925576</v>
+        <v>4.680813775366357</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -812,10 +812,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I12">
-        <v>0.1115303120022872</v>
+        <v>0.2320965879989672</v>
       </c>
       <c r="J12">
-        <v>2.381794643599501</v>
+        <v>2.248563776317626</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -844,10 +844,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I13">
-        <v>0.07004177199996775</v>
+        <v>0.06723470599899883</v>
       </c>
       <c r="J13">
-        <v>1.106830356492333</v>
+        <v>1.073392855705977</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -876,10 +876,10 @@
         <v>0.9999674614743856</v>
       </c>
       <c r="I14">
-        <v>0.01138899900251999</v>
+        <v>0.01247407600021688</v>
       </c>
       <c r="J14">
-        <v>0.528253826350734</v>
+        <v>0.3899330369342945</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -908,10 +908,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I15">
-        <v>0.3943669110012706</v>
+        <v>0.4045976189991052</v>
       </c>
       <c r="J15">
-        <v>39.20242219307084</v>
+        <v>40.92792028131953</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -940,10 +940,10 @@
         <v>0.9990889212827989</v>
       </c>
       <c r="I16">
-        <v>0.2134421289993043</v>
+        <v>0.2254163459983829</v>
       </c>
       <c r="J16">
-        <v>0.8424961736506833</v>
+        <v>0.7958329076375645</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -972,10 +972,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I17">
-        <v>0.2126943479997863</v>
+        <v>0.2120904760013218</v>
       </c>
       <c r="J17">
-        <v>1.223112882812251</v>
+        <v>1.235258291300703</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.01494881599865039</v>
+        <v>0.0129601160006132</v>
       </c>
       <c r="J18">
-        <v>0.4972321430242879</v>
+        <v>0.4141804835426785</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>0.3762919800028612</v>
+        <v>0.3726783589991101</v>
       </c>
       <c r="J19">
-        <v>36.31136415810479</v>
+        <v>36.93452104666254</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1068,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.132345242996962</v>
+        <v>0.1382637329988938</v>
       </c>
       <c r="J20">
-        <v>0.6977863510043363</v>
+        <v>0.7496428572861134</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1100,10 +1100,10 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.1898783489996276</v>
+        <v>0.1882810639981471</v>
       </c>
       <c r="J21">
-        <v>1.166310586104744</v>
+        <v>1.554944516583975</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1132,10 +1132,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I22">
-        <v>0.004703858998254873</v>
+        <v>0.004746763999719406</v>
       </c>
       <c r="J22">
-        <v>0.514413903945343</v>
+        <v>0.4397455350787211</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1164,10 +1164,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I23">
-        <v>0.07787570400250843</v>
+        <v>0.07862527399993269</v>
       </c>
       <c r="J23">
-        <v>8.446756377990676</v>
+        <v>8.331358418793254</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1196,10 +1196,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I24">
-        <v>0.09655772000041907</v>
+        <v>0.1108630390008329</v>
       </c>
       <c r="J24">
-        <v>0.6816658172710403</v>
+        <v>0.6901434958030112</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1228,10 +1228,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I25">
-        <v>0.09527788399645942</v>
+        <v>0.09675844199955463</v>
       </c>
       <c r="J25">
-        <v>1.741220024328237</v>
+        <v>1.660742348539483</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1260,10 +1260,10 @@
         <v>0.9745223344439816</v>
       </c>
       <c r="I26">
-        <v>0.008421070000622422</v>
+        <v>0.009367151000333251</v>
       </c>
       <c r="J26">
-        <v>0.7035695169142112</v>
+        <v>0.705600128565827</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1292,10 +1292,10 @@
         <v>0.9781991878384007</v>
       </c>
       <c r="I27">
-        <v>0.1361730620010349</v>
+        <v>0.1104399979994923</v>
       </c>
       <c r="J27">
-        <v>14.15496556045563</v>
+        <v>14.09270216800924</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1324,10 +1324,10 @@
         <v>0.9838446220324865</v>
       </c>
       <c r="I28">
-        <v>0.09776815799705219</v>
+        <v>0.1079996609987575</v>
       </c>
       <c r="J28">
-        <v>1.495063775202689</v>
+        <v>1.480232141630597</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1356,10 +1356,10 @@
         <v>0.9889564244064973</v>
       </c>
       <c r="I29">
-        <v>0.08110300800035475</v>
+        <v>0.07906552799977362</v>
       </c>
       <c r="J29">
-        <v>0.9792321430277483</v>
+        <v>1.067131376787854</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1388,10 +1388,10 @@
         <v>0.9995973357455227</v>
       </c>
       <c r="I30">
-        <v>0.006916672999068396</v>
+        <v>0.00804335399880074</v>
       </c>
       <c r="J30">
-        <v>0.6306454080765193</v>
+        <v>0.7040982140728264</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1420,10 +1420,10 @@
         <v>0.9997144744377343</v>
       </c>
       <c r="I31">
-        <v>0.1416492669995932</v>
+        <v>0.159163226999226</v>
       </c>
       <c r="J31">
-        <v>19.21614094332041</v>
+        <v>18.97238966964268</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1452,10 +1452,10 @@
         <v>0.9997657226155768</v>
       </c>
       <c r="I32">
-        <v>0.09531347099982668</v>
+        <v>0.09765324700128986</v>
       </c>
       <c r="J32">
-        <v>1.388512115988064</v>
+        <v>1.468161991508577</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1484,10 +1484,10 @@
         <v>0.9948467110058309</v>
       </c>
       <c r="I33">
-        <v>0.06650454900227487</v>
+        <v>0.06567307300065295</v>
       </c>
       <c r="J33">
-        <v>0.948952168871575</v>
+        <v>1.015765944281825</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1516,10 +1516,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I34">
-        <v>0.005071888001111802</v>
+        <v>0.004852211000979878</v>
       </c>
       <c r="J34">
-        <v>0.7129355861586506</v>
+        <v>0.694814414656525</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1548,10 +1548,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I35">
-        <v>0.08388719199865591</v>
+        <v>0.07789639999828069</v>
       </c>
       <c r="J35">
-        <v>8.427511479381717</v>
+        <v>7.454640945534451</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1580,10 +1580,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I36">
-        <v>0.08639386600043508</v>
+        <v>0.1208977499991306</v>
       </c>
       <c r="J36">
-        <v>1.335549745353815</v>
+        <v>1.437096302095374</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1612,10 +1612,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I37">
-        <v>0.08787649299847544</v>
+        <v>0.08662162999826251</v>
       </c>
       <c r="J37">
-        <v>0.9667850769560294</v>
+        <v>1.026200254495869</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/loo_12_models.xlsx
+++ b/dataset/results/loo_12_models.xlsx
@@ -492,10 +492,10 @@
         <v>0.9969674094127446</v>
       </c>
       <c r="I2">
-        <v>0.006491509000625229</v>
+        <v>0.005957350000244332</v>
       </c>
       <c r="J2">
-        <v>0.7906894134808978</v>
+        <v>0.7037340565704876</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -524,10 +524,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>0.0978955800019321</v>
+        <v>0.1041743820023839</v>
       </c>
       <c r="J3">
-        <v>15.86525382774606</v>
+        <v>16.03186096965183</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -556,10 +556,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I4">
-        <v>0.1132245099979627</v>
+        <v>0.09392589100025361</v>
       </c>
       <c r="J4">
-        <v>2.402903062050298</v>
+        <v>2.598933035039167</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -588,10 +588,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I5">
-        <v>0.1855527580009948</v>
+        <v>0.1887038679997204</v>
       </c>
       <c r="J5">
-        <v>1.193208546208887</v>
+        <v>1.187068876937033</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -620,10 +620,10 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0.0104402190008841</v>
+        <v>0.008615163998911157</v>
       </c>
       <c r="J6">
-        <v>0.8198443867736295</v>
+        <v>0.675971939611428</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>0.1336346290008805</v>
+        <v>0.1159897159996035</v>
       </c>
       <c r="J7">
-        <v>16.93507525552767</v>
+        <v>18.73275127485501</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -684,10 +684,10 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.09943619399928139</v>
+        <v>0.2305476219989941</v>
       </c>
       <c r="J8">
-        <v>2.491589287144182</v>
+        <v>2.480682396986706</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -716,10 +716,10 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0.1137324099981925</v>
+        <v>0.115628691000893</v>
       </c>
       <c r="J9">
-        <v>1.124483418959931</v>
+        <v>1.086318877464599</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -748,10 +748,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I10">
-        <v>0.004326718000811525</v>
+        <v>0.003946115997678135</v>
       </c>
       <c r="J10">
-        <v>0.771987244234526</v>
+        <v>0.6556020401390293</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -780,10 +780,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I11">
-        <v>0.0500231129990425</v>
+        <v>0.03841248299795552</v>
       </c>
       <c r="J11">
-        <v>4.680813775366357</v>
+        <v>4.336490433717922</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -812,10 +812,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I12">
-        <v>0.2320965879989672</v>
+        <v>0.1109492619980301</v>
       </c>
       <c r="J12">
-        <v>2.248563776317626</v>
+        <v>2.263177295891201</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -844,10 +844,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I13">
-        <v>0.06723470599899883</v>
+        <v>0.06815544900018722</v>
       </c>
       <c r="J13">
-        <v>1.073392855705977</v>
+        <v>1.054549744942645</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -876,10 +876,10 @@
         <v>0.9999674614743856</v>
       </c>
       <c r="I14">
-        <v>0.01247407600021688</v>
+        <v>0.009725692001666175</v>
       </c>
       <c r="J14">
-        <v>0.3899330369342945</v>
+        <v>0.4038616072314338</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -908,10 +908,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I15">
-        <v>0.4045976189991052</v>
+        <v>0.4070962400001008</v>
       </c>
       <c r="J15">
-        <v>40.92792028131953</v>
+        <v>41.05532780715517</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -940,10 +940,10 @@
         <v>0.9990889212827989</v>
       </c>
       <c r="I16">
-        <v>0.2254163459983829</v>
+        <v>0.2597861050016945</v>
       </c>
       <c r="J16">
-        <v>0.7958329076375645</v>
+        <v>0.8649100766201535</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -972,10 +972,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I17">
-        <v>0.2120904760013218</v>
+        <v>0.2129907329981506</v>
       </c>
       <c r="J17">
-        <v>1.235258291300703</v>
+        <v>1.203023597257442</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.0129601160006132</v>
+        <v>0.01410424699861323</v>
       </c>
       <c r="J18">
-        <v>0.4141804835426785</v>
+        <v>0.4176122437067014</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>0.3726783589991101</v>
+        <v>0.3729423379991204</v>
       </c>
       <c r="J19">
-        <v>36.93452104666254</v>
+        <v>37.4332168381183</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1068,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.1382637329988938</v>
+        <v>0.1668176650018722</v>
       </c>
       <c r="J20">
-        <v>0.7496428572861134</v>
+        <v>0.7820114790644896</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1100,10 +1100,10 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.1882810639981471</v>
+        <v>0.1884277109966206</v>
       </c>
       <c r="J21">
-        <v>1.554944516583975</v>
+        <v>1.187036988939122</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1132,10 +1132,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I22">
-        <v>0.004746763999719406</v>
+        <v>0.004605179001373472</v>
       </c>
       <c r="J22">
-        <v>0.4397455350787211</v>
+        <v>0.4394642854428955</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1164,10 +1164,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I23">
-        <v>0.07862527399993269</v>
+        <v>0.07950842799982638</v>
       </c>
       <c r="J23">
-        <v>8.331358418793254</v>
+        <v>8.700998088378192</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1196,10 +1196,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I24">
-        <v>0.1108630390008329</v>
+        <v>0.1103801569988718</v>
       </c>
       <c r="J24">
-        <v>0.6901434958030112</v>
+        <v>0.6822461723366323</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1228,10 +1228,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I25">
-        <v>0.09675844199955463</v>
+        <v>0.09735454900146578</v>
       </c>
       <c r="J25">
-        <v>1.660742348539483</v>
+        <v>1.355681760918631</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1260,10 +1260,10 @@
         <v>0.9745223344439816</v>
       </c>
       <c r="I26">
-        <v>0.009367151000333251</v>
+        <v>0.008633318000647705</v>
       </c>
       <c r="J26">
-        <v>0.705600128565827</v>
+        <v>0.7084815052269046</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1292,10 +1292,10 @@
         <v>0.9781991878384007</v>
       </c>
       <c r="I27">
-        <v>0.1104399979994923</v>
+        <v>0.1286771710001631</v>
       </c>
       <c r="J27">
-        <v>14.09270216800924</v>
+        <v>13.81427933684252</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1324,10 +1324,10 @@
         <v>0.9838446220324865</v>
       </c>
       <c r="I28">
-        <v>0.1079996609987575</v>
+        <v>0.2397755029996915</v>
       </c>
       <c r="J28">
-        <v>1.480232141630597</v>
+        <v>1.713487881251964</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1356,10 +1356,10 @@
         <v>0.9889564244064973</v>
       </c>
       <c r="I29">
-        <v>0.07906552799977362</v>
+        <v>0.08014323599854833</v>
       </c>
       <c r="J29">
-        <v>1.067131376787854</v>
+        <v>0.981096300907963</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1388,10 +1388,10 @@
         <v>0.9995973357455227</v>
       </c>
       <c r="I30">
-        <v>0.00804335399880074</v>
+        <v>0.008300686000438873</v>
       </c>
       <c r="J30">
-        <v>0.7040982140728264</v>
+        <v>0.7058042103603747</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1420,10 +1420,10 @@
         <v>0.9997144744377343</v>
       </c>
       <c r="I31">
-        <v>0.159163226999226</v>
+        <v>0.1587149210026837</v>
       </c>
       <c r="J31">
-        <v>18.97238966964268</v>
+        <v>18.92638584065156</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1452,10 +1452,10 @@
         <v>0.9997657226155768</v>
       </c>
       <c r="I32">
-        <v>0.09765324700128986</v>
+        <v>0.2412383209994005</v>
       </c>
       <c r="J32">
-        <v>1.468161991508577</v>
+        <v>1.531827806223989</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1484,10 +1484,10 @@
         <v>0.9948467110058309</v>
       </c>
       <c r="I33">
-        <v>0.06567307300065295</v>
+        <v>0.06614660000195727</v>
       </c>
       <c r="J33">
-        <v>1.015765944281825</v>
+        <v>1.046147960495342</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1516,10 +1516,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I34">
-        <v>0.004852211000979878</v>
+        <v>0.00548359300228185</v>
       </c>
       <c r="J34">
-        <v>0.694814414656525</v>
+        <v>0.6913195165350549</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1548,10 +1548,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I35">
-        <v>0.07789639999828069</v>
+        <v>0.08419754399801604</v>
       </c>
       <c r="J35">
-        <v>7.454640945534451</v>
+        <v>9.586417729910956</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1580,10 +1580,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I36">
-        <v>0.1208977499991306</v>
+        <v>0.08652222499949858</v>
       </c>
       <c r="J36">
-        <v>1.437096302095374</v>
+        <v>1.378498725490336</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1612,10 +1612,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I37">
-        <v>0.08662162999826251</v>
+        <v>0.08740940500138095</v>
       </c>
       <c r="J37">
-        <v>1.026200254495869</v>
+        <v>1.370779338165968</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/loo_12_models.xlsx
+++ b/dataset/results/loo_12_models.xlsx
@@ -492,10 +492,10 @@
         <v>0.9969674094127446</v>
       </c>
       <c r="I2">
-        <v>0.005957350000244332</v>
+        <v>0.006008242000461905</v>
       </c>
       <c r="J2">
-        <v>0.7037340565704876</v>
+        <v>0.7258220657790009</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -524,10 +524,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>0.1041743820023839</v>
+        <v>0.1000213209990761</v>
       </c>
       <c r="J3">
-        <v>16.03186096965183</v>
+        <v>15.86382206615242</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -556,10 +556,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I4">
-        <v>0.09392589100025361</v>
+        <v>0.09658765600033803</v>
       </c>
       <c r="J4">
-        <v>2.598933035039167</v>
+        <v>2.450241072206061</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -588,10 +588,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I5">
-        <v>0.1887038679997204</v>
+        <v>0.1878472640000837</v>
       </c>
       <c r="J5">
-        <v>1.187068876937033</v>
+        <v>1.078362883469467</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -620,10 +620,10 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0.008615163998911157</v>
+        <v>0.0104264889996557</v>
       </c>
       <c r="J6">
-        <v>0.675971939611428</v>
+        <v>0.8363029346768673</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>0.1159897159996035</v>
+        <v>0.137257946000318</v>
       </c>
       <c r="J7">
-        <v>18.73275127485501</v>
+        <v>17.55844706557192</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -684,10 +684,10 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.2305476219989941</v>
+        <v>0.1054298709987052</v>
       </c>
       <c r="J8">
-        <v>2.480682396986706</v>
+        <v>2.460438774589272</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -716,10 +716,10 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0.115628691000893</v>
+        <v>0.1151124980005989</v>
       </c>
       <c r="J9">
-        <v>1.086318877464599</v>
+        <v>1.272783163362967</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -748,10 +748,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I10">
-        <v>0.003946115997678135</v>
+        <v>0.004428246000315994</v>
       </c>
       <c r="J10">
-        <v>0.6556020401390293</v>
+        <v>0.789749361381243</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -780,10 +780,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I11">
-        <v>0.03841248299795552</v>
+        <v>0.05167253500076185</v>
       </c>
       <c r="J11">
-        <v>4.336490433717922</v>
+        <v>5.338771684039655</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -812,10 +812,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I12">
-        <v>0.1109492619980301</v>
+        <v>0.3085978830004024</v>
       </c>
       <c r="J12">
-        <v>2.263177295891201</v>
+        <v>2.758714285800106</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -844,10 +844,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I13">
-        <v>0.06815544900018722</v>
+        <v>0.06879046500034747</v>
       </c>
       <c r="J13">
-        <v>1.054549744942645</v>
+        <v>3.197417729041968</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -876,10 +876,10 @@
         <v>0.9999674614743856</v>
       </c>
       <c r="I14">
-        <v>0.009725692001666175</v>
+        <v>0.009977829000490601</v>
       </c>
       <c r="J14">
-        <v>0.4038616072314338</v>
+        <v>0.4099891584144421</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -908,10 +908,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I15">
-        <v>0.4070962400001008</v>
+        <v>0.3876137609986472</v>
       </c>
       <c r="J15">
-        <v>41.05532780715517</v>
+        <v>38.63068175920786</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -940,10 +940,10 @@
         <v>0.9990889212827989</v>
       </c>
       <c r="I16">
-        <v>0.2597861050016945</v>
+        <v>0.1922716219996801</v>
       </c>
       <c r="J16">
-        <v>0.8649100766201535</v>
+        <v>0.8259139031461203</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -972,10 +972,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I17">
-        <v>0.2129907329981506</v>
+        <v>0.2110591560012836</v>
       </c>
       <c r="J17">
-        <v>1.203023597257442</v>
+        <v>1.240375637484694</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.01410424699861323</v>
+        <v>0.01240734599923599</v>
       </c>
       <c r="J18">
-        <v>0.4176122437067014</v>
+        <v>0.4149598207360974</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>0.3729423379991204</v>
+        <v>0.3611910409999837</v>
       </c>
       <c r="J19">
-        <v>37.4332168381183</v>
+        <v>36.92386607145654</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1068,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.1668176650018722</v>
+        <v>0.1318186579992471</v>
       </c>
       <c r="J20">
-        <v>0.7820114790644896</v>
+        <v>0.7271575253405305</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1100,10 +1100,10 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.1884277109966206</v>
+        <v>0.1872214830000303</v>
       </c>
       <c r="J21">
-        <v>1.187036988939122</v>
+        <v>1.189904974914813</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1132,10 +1132,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I22">
-        <v>0.004605179001373472</v>
+        <v>0.004618271001163521</v>
       </c>
       <c r="J22">
-        <v>0.4394642854428955</v>
+        <v>0.4442818881587449</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1164,10 +1164,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I23">
-        <v>0.07950842799982638</v>
+        <v>0.0760087510006997</v>
       </c>
       <c r="J23">
-        <v>8.700998088378192</v>
+        <v>8.186842475127804</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1196,10 +1196,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I24">
-        <v>0.1103801569988718</v>
+        <v>0.1017057429999113</v>
       </c>
       <c r="J24">
-        <v>0.6822461723366323</v>
+        <v>0.6442225769985401</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1228,10 +1228,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I25">
-        <v>0.09735454900146578</v>
+        <v>0.0957372659995599</v>
       </c>
       <c r="J25">
-        <v>1.355681760918631</v>
+        <v>1.661904335907486</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1260,10 +1260,10 @@
         <v>0.9745223344439816</v>
       </c>
       <c r="I26">
-        <v>0.008633318000647705</v>
+        <v>0.008865849000358139</v>
       </c>
       <c r="J26">
-        <v>0.7084815052269046</v>
+        <v>0.698672832241959</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1292,10 +1292,10 @@
         <v>0.9781991878384007</v>
       </c>
       <c r="I27">
-        <v>0.1286771710001631</v>
+        <v>0.122350722000192</v>
       </c>
       <c r="J27">
-        <v>13.81427933684252</v>
+        <v>13.53881441329985</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1324,10 +1324,10 @@
         <v>0.9838446220324865</v>
       </c>
       <c r="I28">
-        <v>0.2397755029996915</v>
+        <v>0.09925197200027469</v>
       </c>
       <c r="J28">
-        <v>1.713487881251964</v>
+        <v>1.408177296274962</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1356,10 +1356,10 @@
         <v>0.9889564244064973</v>
       </c>
       <c r="I29">
-        <v>0.08014323599854833</v>
+        <v>0.08006626299902564</v>
       </c>
       <c r="J29">
-        <v>0.981096300907963</v>
+        <v>1.505393494686099</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1388,10 +1388,10 @@
         <v>0.9995973357455227</v>
       </c>
       <c r="I30">
-        <v>0.008300686000438873</v>
+        <v>0.008048219000556855</v>
       </c>
       <c r="J30">
-        <v>0.7058042103603747</v>
+        <v>0.7028456635378795</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1420,10 +1420,10 @@
         <v>0.9997144744377343</v>
       </c>
       <c r="I31">
-        <v>0.1587149210026837</v>
+        <v>0.167994206000003</v>
       </c>
       <c r="J31">
-        <v>18.92638584065156</v>
+        <v>18.67125637758994</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1452,10 +1452,10 @@
         <v>0.9997657226155768</v>
       </c>
       <c r="I32">
-        <v>0.2412383209994005</v>
+        <v>0.09651940900039335</v>
       </c>
       <c r="J32">
-        <v>1.531827806223989</v>
+        <v>1.468755739579694</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1484,10 +1484,10 @@
         <v>0.9948467110058309</v>
       </c>
       <c r="I33">
-        <v>0.06614660000195727</v>
+        <v>0.06540351799958444</v>
       </c>
       <c r="J33">
-        <v>1.046147960495342</v>
+        <v>1.057674107498166</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1516,10 +1516,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I34">
-        <v>0.00548359300228185</v>
+        <v>0.02661878599974443</v>
       </c>
       <c r="J34">
-        <v>0.6913195165350549</v>
+        <v>0.6328743614974475</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1548,10 +1548,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I35">
-        <v>0.08419754399801604</v>
+        <v>0.05569085499882931</v>
       </c>
       <c r="J35">
-        <v>9.586417729910956</v>
+        <v>7.165850765701106</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1580,10 +1580,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I36">
-        <v>0.08652222499949858</v>
+        <v>0.1122767130000284</v>
       </c>
       <c r="J36">
-        <v>1.378498725490336</v>
+        <v>1.363904336627382</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1612,10 +1612,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I37">
-        <v>0.08740940500138095</v>
+        <v>0.08716113900118216</v>
       </c>
       <c r="J37">
-        <v>1.370779338165968</v>
+        <v>0.9560682398693401</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/loo_12_models.xlsx
+++ b/dataset/results/loo_12_models.xlsx
@@ -492,10 +492,10 @@
         <v>0.9969674094127446</v>
       </c>
       <c r="I2">
-        <v>0.006008242000461905</v>
+        <v>0.007186103999629267</v>
       </c>
       <c r="J2">
-        <v>0.7258220657790009</v>
+        <v>1.076631378407688</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -524,10 +524,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>0.1000213209990761</v>
+        <v>0.1032397809995018</v>
       </c>
       <c r="J3">
-        <v>15.86382206615242</v>
+        <v>15.30624489862243</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -556,10 +556,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I4">
-        <v>0.09658765600033803</v>
+        <v>0.09934950199931336</v>
       </c>
       <c r="J4">
-        <v>2.450241072206061</v>
+        <v>2.494871173253995</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -588,10 +588,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I5">
-        <v>0.1878472640000837</v>
+        <v>0.1850991199989949</v>
       </c>
       <c r="J5">
-        <v>1.078362883469467</v>
+        <v>1.228714285509935</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -620,10 +620,10 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0.0104264889996557</v>
+        <v>0.0107802790007554</v>
       </c>
       <c r="J6">
-        <v>0.8363029346768673</v>
+        <v>0.8119783155869263</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>0.137257946000318</v>
+        <v>0.120524617999763</v>
       </c>
       <c r="J7">
-        <v>17.55844706557192</v>
+        <v>17.1573227044528</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -684,10 +684,10 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.1054298709987052</v>
+        <v>0.1278748299992003</v>
       </c>
       <c r="J8">
-        <v>2.460438774589272</v>
+        <v>2.532499362290281</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -716,10 +716,10 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0.1151124980005989</v>
+        <v>0.113458437999725</v>
       </c>
       <c r="J9">
-        <v>1.272783163362967</v>
+        <v>4.987136479457502</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -748,10 +748,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I10">
-        <v>0.004428246000315994</v>
+        <v>0.005368434000047273</v>
       </c>
       <c r="J10">
-        <v>0.789749361381243</v>
+        <v>0.7462308670311563</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -780,10 +780,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I11">
-        <v>0.05167253500076185</v>
+        <v>0.05323826300082146</v>
       </c>
       <c r="J11">
-        <v>5.338771684039655</v>
+        <v>5.289692601726696</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -812,10 +812,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I12">
-        <v>0.3085978830004024</v>
+        <v>0.09668208100083575</v>
       </c>
       <c r="J12">
-        <v>2.758714285800106</v>
+        <v>2.332028699055051</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -844,10 +844,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I13">
-        <v>0.06879046500034747</v>
+        <v>0.06683456000064325</v>
       </c>
       <c r="J13">
-        <v>3.197417729041968</v>
+        <v>1.088503187920465</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -876,10 +876,10 @@
         <v>0.9999674614743856</v>
       </c>
       <c r="I14">
-        <v>0.009977829000490601</v>
+        <v>0.01174872100091306</v>
       </c>
       <c r="J14">
-        <v>0.4099891584144421</v>
+        <v>0.4895446425377616</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -908,10 +908,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I15">
-        <v>0.3876137609986472</v>
+        <v>0.3890657089996239</v>
       </c>
       <c r="J15">
-        <v>38.63068175920786</v>
+        <v>39.27520790906486</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -940,10 +940,10 @@
         <v>0.9990889212827989</v>
       </c>
       <c r="I16">
-        <v>0.1922716219996801</v>
+        <v>0.1552450460003456</v>
       </c>
       <c r="J16">
-        <v>0.8259139031461203</v>
+        <v>0.8197672189323515</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -972,10 +972,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I17">
-        <v>0.2110591560012836</v>
+        <v>0.2080317549989559</v>
       </c>
       <c r="J17">
-        <v>1.240375637484694</v>
+        <v>1.473368622462621</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.01240734599923599</v>
+        <v>0.01267242900030396</v>
       </c>
       <c r="J18">
-        <v>0.4149598207360974</v>
+        <v>0.4016320146120608</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>0.3611910409999837</v>
+        <v>0.3585823579996941</v>
       </c>
       <c r="J19">
-        <v>36.92386607145654</v>
+        <v>35.96458801017174</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1068,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.1318186579992471</v>
+        <v>0.1369382859993493</v>
       </c>
       <c r="J20">
-        <v>0.7271575253405305</v>
+        <v>0.7969630093277968</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1100,10 +1100,10 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.1872214830000303</v>
+        <v>0.1844439739998052</v>
       </c>
       <c r="J21">
-        <v>1.189904974914813</v>
+        <v>1.353929846749341</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1132,10 +1132,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I22">
-        <v>0.004618271001163521</v>
+        <v>0.004790973000126542</v>
       </c>
       <c r="J22">
-        <v>0.4442818881587449</v>
+        <v>0.4466900514782946</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1164,10 +1164,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I23">
-        <v>0.0760087510006997</v>
+        <v>0.07687301100122568</v>
       </c>
       <c r="J23">
-        <v>8.186842475127804</v>
+        <v>8.706064412373443</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1196,10 +1196,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I24">
-        <v>0.1017057429999113</v>
+        <v>0.0849137340010202</v>
       </c>
       <c r="J24">
-        <v>0.6442225769985401</v>
+        <v>0.6910567595714754</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1228,10 +1228,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I25">
-        <v>0.0957372659995599</v>
+        <v>0.09473514899946167</v>
       </c>
       <c r="J25">
-        <v>1.661904335907486</v>
+        <v>1.623834821527583</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1260,10 +1260,10 @@
         <v>0.9745223344439816</v>
       </c>
       <c r="I26">
-        <v>0.008865849000358139</v>
+        <v>0.008978628000477329</v>
       </c>
       <c r="J26">
-        <v>0.698672832241959</v>
+        <v>0.7027499995441461</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1292,10 +1292,10 @@
         <v>0.9781991878384007</v>
       </c>
       <c r="I27">
-        <v>0.122350722000192</v>
+        <v>0.1325822160015377</v>
       </c>
       <c r="J27">
-        <v>13.53881441329985</v>
+        <v>13.80101785770774</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1324,10 +1324,10 @@
         <v>0.9838446220324865</v>
       </c>
       <c r="I28">
-        <v>0.09925197200027469</v>
+        <v>0.09626794600080757</v>
       </c>
       <c r="J28">
-        <v>1.408177296274962</v>
+        <v>1.475202168421674</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1356,10 +1356,10 @@
         <v>0.9889564244064973</v>
       </c>
       <c r="I29">
-        <v>0.08006626299902564</v>
+        <v>0.07949707000079798</v>
       </c>
       <c r="J29">
-        <v>1.505393494686099</v>
+        <v>1.040677933379273</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1388,10 +1388,10 @@
         <v>0.9995973357455227</v>
       </c>
       <c r="I30">
-        <v>0.008048219000556855</v>
+        <v>0.008367385000383365</v>
       </c>
       <c r="J30">
-        <v>0.7028456635378795</v>
+        <v>0.6853125000816362</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1420,10 +1420,10 @@
         <v>0.9997144744377343</v>
       </c>
       <c r="I31">
-        <v>0.167994206000003</v>
+        <v>0.1547536670004774</v>
       </c>
       <c r="J31">
-        <v>18.67125637758994</v>
+        <v>18.61074936326132</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1452,10 +1452,10 @@
         <v>0.9997657226155768</v>
       </c>
       <c r="I32">
-        <v>0.09651940900039335</v>
+        <v>0.09647758900064218</v>
       </c>
       <c r="J32">
-        <v>1.468755739579694</v>
+        <v>1.475873724692584</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1484,10 +1484,10 @@
         <v>0.9948467110058309</v>
       </c>
       <c r="I33">
-        <v>0.06540351799958444</v>
+        <v>0.06569661100002122</v>
       </c>
       <c r="J33">
-        <v>1.057674107498166</v>
+        <v>2.321556122779486</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1516,10 +1516,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I34">
-        <v>0.02661878599974443</v>
+        <v>0.04603234100068221</v>
       </c>
       <c r="J34">
-        <v>0.6328743614974475</v>
+        <v>0.6970121169578473</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1548,10 +1548,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I35">
-        <v>0.05569085499882931</v>
+        <v>0.06966604700028256</v>
       </c>
       <c r="J35">
-        <v>7.165850765701106</v>
+        <v>6.876845026342881</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1580,10 +1580,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I36">
-        <v>0.1122767130000284</v>
+        <v>0.11206853800104</v>
       </c>
       <c r="J36">
-        <v>1.363904336627382</v>
+        <v>1.385117346968883</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1612,10 +1612,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I37">
-        <v>0.08716113900118216</v>
+        <v>0.0865620280001167</v>
       </c>
       <c r="J37">
-        <v>0.9560682398693401</v>
+        <v>1.335457908430262</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/results/loo_12_models.xlsx
+++ b/dataset/results/loo_12_models.xlsx
@@ -492,10 +492,10 @@
         <v>0.9969674094127446</v>
       </c>
       <c r="I2">
-        <v>0.007186103999629267</v>
+        <v>0.005947049001406413</v>
       </c>
       <c r="J2">
-        <v>1.076631378407688</v>
+        <v>0.6841881384166392</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -524,10 +524,10 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>0.1032397809995018</v>
+        <v>0.1030013239978871</v>
       </c>
       <c r="J3">
-        <v>15.30624489862243</v>
+        <v>15.47110012751898</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -556,10 +556,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I4">
-        <v>0.09934950199931336</v>
+        <v>0.1114203889992496</v>
       </c>
       <c r="J4">
-        <v>2.494871173253995</v>
+        <v>2.471327169754362</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -588,10 +588,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I5">
-        <v>0.1850991199989949</v>
+        <v>0.1858571299999312</v>
       </c>
       <c r="J5">
-        <v>1.228714285509935</v>
+        <v>1.062619897923895</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -620,10 +620,10 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>0.0107802790007554</v>
+        <v>0.01052223999795387</v>
       </c>
       <c r="J6">
-        <v>0.8119783155869263</v>
+        <v>0.7938067599344341</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -652,10 +652,10 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>0.120524617999763</v>
+        <v>0.1415599079991807</v>
       </c>
       <c r="J7">
-        <v>17.1573227044528</v>
+        <v>16.65239222125003</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -684,10 +684,10 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>0.1278748299992003</v>
+        <v>0.1872488350018102</v>
       </c>
       <c r="J8">
-        <v>2.532499362290281</v>
+        <v>2.482610968901118</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -716,10 +716,10 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>0.113458437999725</v>
+        <v>0.1139326500015159</v>
       </c>
       <c r="J9">
-        <v>4.987136479457502</v>
+        <v>1.176493622885889</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -748,10 +748,10 @@
         <v>0.6063001093294461</v>
       </c>
       <c r="I10">
-        <v>0.005368434000047273</v>
+        <v>0.004994987000827678</v>
       </c>
       <c r="J10">
-        <v>0.7462308670311563</v>
+        <v>0.7639872453127078</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -780,10 +780,10 @@
         <v>0.9579309402332361</v>
       </c>
       <c r="I11">
-        <v>0.05323826300082146</v>
+        <v>0.05235640300088562</v>
       </c>
       <c r="J11">
-        <v>5.289692601726696</v>
+        <v>5.10450063859248</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -812,10 +812,10 @@
         <v>0.9131587424510621</v>
       </c>
       <c r="I12">
-        <v>0.09668208100083575</v>
+        <v>0.1688585219999368</v>
       </c>
       <c r="J12">
-        <v>2.332028699055051</v>
+        <v>4.412191325005848</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -844,10 +844,10 @@
         <v>0.5178115889212828</v>
       </c>
       <c r="I13">
-        <v>0.06683456000064325</v>
+        <v>0.07057402300051763</v>
       </c>
       <c r="J13">
-        <v>1.088503187920465</v>
+        <v>1.246541452409084</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -876,10 +876,10 @@
         <v>0.9999674614743856</v>
       </c>
       <c r="I14">
-        <v>0.01174872100091306</v>
+        <v>0.01232971200079191</v>
       </c>
       <c r="J14">
-        <v>0.4895446425377616</v>
+        <v>0.518885202632655</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -908,10 +908,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I15">
-        <v>0.3890657089996239</v>
+        <v>0.40223866100132</v>
       </c>
       <c r="J15">
-        <v>39.27520790906486</v>
+        <v>39.58460969238795</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -940,10 +940,10 @@
         <v>0.9990889212827989</v>
       </c>
       <c r="I16">
-        <v>0.1552450460003456</v>
+        <v>0.2746371129978797</v>
       </c>
       <c r="J16">
-        <v>0.8197672189323515</v>
+        <v>0.8560344384728078</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -972,10 +972,10 @@
         <v>0.9999999999999999</v>
       </c>
       <c r="I17">
-        <v>0.2080317549989559</v>
+        <v>0.2107335119981144</v>
       </c>
       <c r="J17">
-        <v>1.473368622462621</v>
+        <v>1.254323977690899</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -1004,10 +1004,10 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.01267242900030396</v>
+        <v>0.01227959799871314</v>
       </c>
       <c r="J18">
-        <v>0.4016320146120608</v>
+        <v>0.4329910705898644</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -1036,10 +1036,10 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>0.3585823579996941</v>
+        <v>0.3718699729979562</v>
       </c>
       <c r="J19">
-        <v>35.96458801017174</v>
+        <v>37.65490816235519</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -1068,10 +1068,10 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.1369382859993493</v>
+        <v>0.1592397919994255</v>
       </c>
       <c r="J20">
-        <v>0.7969630093277968</v>
+        <v>0.7332531873655579</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -1100,10 +1100,10 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.1844439739998052</v>
+        <v>0.1871654790011235</v>
       </c>
       <c r="J21">
-        <v>1.353929846749341</v>
+        <v>1.21382142693545</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -1132,10 +1132,10 @@
         <v>0.9384647672844649</v>
       </c>
       <c r="I22">
-        <v>0.004790973000126542</v>
+        <v>0.004654018997825915</v>
       </c>
       <c r="J22">
-        <v>0.4466900514782946</v>
+        <v>0.4303016599546287</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -1164,10 +1164,10 @@
         <v>0.9402966862765514</v>
       </c>
       <c r="I23">
-        <v>0.07687301100122568</v>
+        <v>0.07734194799922989</v>
       </c>
       <c r="J23">
-        <v>8.706064412373443</v>
+        <v>8.49870918398442</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -1196,10 +1196,10 @@
         <v>0.5440051020408164</v>
       </c>
       <c r="I24">
-        <v>0.0849137340010202</v>
+        <v>0.1127231959981145</v>
       </c>
       <c r="J24">
-        <v>0.6910567595714754</v>
+        <v>0.6187659432633118</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -1228,10 +1228,10 @@
         <v>0.819830929820908</v>
       </c>
       <c r="I25">
-        <v>0.09473514899946167</v>
+        <v>0.09618018000037409</v>
       </c>
       <c r="J25">
-        <v>1.623834821527583</v>
+        <v>1.370945791937369</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -1260,10 +1260,10 @@
         <v>0.9745223344439816</v>
       </c>
       <c r="I26">
-        <v>0.008978628000477329</v>
+        <v>0.008618687999842223</v>
       </c>
       <c r="J26">
-        <v>0.7027499995441461</v>
+        <v>0.7024751279719308</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -1292,10 +1292,10 @@
         <v>0.9781991878384007</v>
       </c>
       <c r="I27">
-        <v>0.1325822160015377</v>
+        <v>0.1190859429989359</v>
       </c>
       <c r="J27">
-        <v>13.80101785770774</v>
+        <v>13.92841709136463</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -1324,10 +1324,10 @@
         <v>0.9838446220324865</v>
       </c>
       <c r="I28">
-        <v>0.09626794600080757</v>
+        <v>0.1078560189998825</v>
       </c>
       <c r="J28">
-        <v>1.475202168421674</v>
+        <v>1.452526786885514</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -1356,10 +1356,10 @@
         <v>0.9889564244064973</v>
       </c>
       <c r="I29">
-        <v>0.07949707000079798</v>
+        <v>0.07996384400030365</v>
       </c>
       <c r="J29">
-        <v>1.040677933379273</v>
+        <v>0.9462346938283989</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -1388,10 +1388,10 @@
         <v>0.9995973357455227</v>
       </c>
       <c r="I30">
-        <v>0.008367385000383365</v>
+        <v>0.006788362999941455</v>
       </c>
       <c r="J30">
-        <v>0.6853125000816362</v>
+        <v>0.6215140302276491</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -1420,10 +1420,10 @@
         <v>0.9997144744377343</v>
       </c>
       <c r="I31">
-        <v>0.1547536670004774</v>
+        <v>0.1404550810002547</v>
       </c>
       <c r="J31">
-        <v>18.61074936326132</v>
+        <v>18.950135842381</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1452,10 +1452,10 @@
         <v>0.9997657226155768</v>
       </c>
       <c r="I32">
-        <v>0.09647758900064218</v>
+        <v>0.1468254720020923</v>
       </c>
       <c r="J32">
-        <v>1.475873724692584</v>
+        <v>1.656799106652271</v>
       </c>
     </row>
     <row r="33" spans="1:10">
@@ -1484,10 +1484,10 @@
         <v>0.9948467110058309</v>
       </c>
       <c r="I33">
-        <v>0.06569661100002122</v>
+        <v>0.06511514899830217</v>
       </c>
       <c r="J33">
-        <v>2.321556122779486</v>
+        <v>0.9219100770585974</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -1516,10 +1516,10 @@
         <v>0.915163929092045</v>
       </c>
       <c r="I34">
-        <v>0.04603234100068221</v>
+        <v>0.004356301000370877</v>
       </c>
       <c r="J34">
-        <v>0.6970121169578473</v>
+        <v>0.6155459167140569</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -1548,10 +1548,10 @@
         <v>0.8986929274260725</v>
       </c>
       <c r="I35">
-        <v>0.06966604700028256</v>
+        <v>0.05563695299861138</v>
       </c>
       <c r="J35">
-        <v>6.876845026342881</v>
+        <v>7.177315050823233</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -1580,10 +1580,10 @@
         <v>0.874400477665556</v>
       </c>
       <c r="I36">
-        <v>0.11206853800104</v>
+        <v>0.1304415130034613</v>
       </c>
       <c r="J36">
-        <v>1.385117346968883</v>
+        <v>1.689482142141134</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -1612,10 +1612,10 @@
         <v>0.8772288890045814</v>
       </c>
       <c r="I37">
-        <v>0.0865620280001167</v>
+        <v>0.08599821699681343</v>
       </c>
       <c r="J37">
-        <v>1.335457908430262</v>
+        <v>0.9024604586167178</v>
       </c>
     </row>
   </sheetData>
